--- a/week 5/Report/report.xlsx
+++ b/week 5/Report/report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dark7\Downloads\mindx-engineer-onboarding.20261205\docs\plans\week-5\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MindxTech\.Mindx-Challenge\Training\training-remote\week 5\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E70F8C-A9D1-4739-82E9-CFEB1E1C1AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D1C5C5-7307-4172-B225-8A9BDC776F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="439">
   <si>
     <t>Active</t>
   </si>
@@ -1281,19 +1281,168 @@
     <t>State</t>
   </si>
   <si>
-    <t>PHÂN TÍCH
-- Nhóm Other chiếm tỷ lệ cao nhất, cho thấy quy tắc phân loại hiện tại vẫn chưa bao phủ hết các loại ticket.
-- Enrollment Issue là nhóm vấn đề phổ biến nhất trong các nhóm đã được phân loại.
-- Account Access Issue và Email Issue xuất hiện thường xuyên và phù hợp để tự động hóa xử lý.
-- CRM Issue có số lượng thấp hơn và thường cần kiểm tra thủ công.
-- Cần bổ sung thêm quy tắc phân loại để giảm số lượng ticket thuộc nhóm Other.</t>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Enrollment Issue là nhóm vấn đề phổ biến nhất trong các nhóm đã được phân loại.</t>
+  </si>
+  <si>
+    <t>Nhóm Other chiếm tỷ lệ rất cao (61.83%), cho thấy quy tắc phân loại hiện tại chưa bao phủ hết các loại ticket.</t>
+  </si>
+  <si>
+    <t>Account Access Issue và Email Issue có số lượng tương đương nhau và xuất hiện thường xuyên.</t>
+  </si>
+  <si>
+    <t>CRM Issue xuất hiện ít hơn và thường yêu cầu xử lý chuyên biệt.</t>
+  </si>
+  <si>
+    <t>Cần mở rộng bộ quy tắc phân loại để giảm số lượng ticket thuộc nhóm Other.</t>
+  </si>
+  <si>
+    <t>Ticket High Priority chiếm tỷ lệ lớn nhất với 42 ticket.</t>
+  </si>
+  <si>
+    <t>Số lượng ticket Low Priority và Urgent gần tương đương nhau, cho thấy khối lượng công việc được phân bổ ở nhiều mức độ ưu tiên khác nhau.</t>
+  </si>
+  <si>
+    <t>Ticket Medium Priority xuất hiện ít hơn đáng kể so với các mức ưu tiên còn lại.</t>
+  </si>
+  <si>
+    <t>KEY FINDINGS</t>
+  </si>
+  <si>
+    <t>Rà soát lại quy trình cập nhật trạng thái ticket để đảm bảo các trạng thái được phản ánh chính xác trong hệ thống.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mở rộng và cải thiện bộ quy tắc phân loại để giảm số lượng ticket thuộc nhóm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Other</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ưu tiên xây dựng các quy trình tự động hóa cho các ticket thuộc nhóm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Account Access Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Email Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> do đây là các vấn đề xuất hiện thường xuyên và có quy trình xử lý tương đối rõ ràng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xây dựng tài liệu hướng dẫn (Knowledge Base) cho các vấn đề liên quan đến </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Enrollment Issue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> nhằm giảm thời gian hỗ trợ và tăng khả năng tự xử lý của người dùng.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enrollment Issue là nhóm vấn đề phổ biến nhất trong các nhóm đã được phân loại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CRM Issue có số lượng thấp Hơn và thường cần kiểm tra thủ công.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cần bổ sung thêm quy tắc phân loại để giảm số lượng ticket thuộc nhóm Other.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nhóm Other chiếm tỷ lệ cao nhất, cho thấy quy tắc phân loại hiện tại vẫn chưa bao phủ hết các loại ticket.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Account Access Issue và Email Issue xuất hiện thường xuyên và phù hợp để tự động hóa xử lý.</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>RECOMMENDATIONS</t>
+  </si>
+  <si>
+    <t>- 61.83% ticket được phân loại vào nhóm Other, đây là cơ hội cải thiện lớn nhất cho hệ thống phân loại.</t>
+  </si>
+  <si>
+    <t>- Các ticket liên quan đến Enrollment, Account Access và Email chiếm tỷ lệ đáng kể trong tổng số ticket đã được phân loại.</t>
+  </si>
+  <si>
+    <t>- Dữ liệu cho thấy phần lớn ticket tập trung vào một số nhóm vấn đề nhất định, phù hợp để xây dựng quy trình hỗ trợ chuẩn hóa.</t>
+  </si>
+  <si>
+    <t>- Các nhóm vấn đề lặp lại nhiều lần cho thấy tiềm năng áp dụng tự động hóa nhằm giảm khối lượng xử lý thủ công.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1313,6 +1462,26 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1356,7 +1525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1371,10 +1540,24 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1426,8 +1609,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Category</a:t>
+              <a:rPr lang="vi-VN"/>
+              <a:t>Biểu đồ tỉ lệ xuất hiện loại ticket</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1464,34 +1647,129 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Category Report'!$B$1</c:f>
+              <c:f>'Category Report'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Count</c:v>
+                  <c:v>Percent</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
             <c:strRef>
               <c:f>'Category Report'!$A$2:$A$8</c:f>
@@ -1523,37 +1801,37 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Category Report'!$B$2:$B$8</c:f>
+              <c:f>'Category Report'!$C$2:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>81</c:v>
+                  <c:v>61.83</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13</c:v>
+                  <c:v>9.92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11</c:v>
+                  <c:v>8.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>8.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9</c:v>
+                  <c:v>6.87</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>2.29</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>2.29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D72A-4B7A-8471-4FC287624078}"/>
+              <c16:uniqueId val="{00000000-54FC-4353-82B2-6111EDFD7FE8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1564,119 +1842,10 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="2098394448"/>
-        <c:axId val="2098393488"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2098394448"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2098393488"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2098393488"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2098394448"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1685,6 +1854,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1788,7 +1988,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="vi-VN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2140,7 +2340,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="vi-VN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2490,7 +2690,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2547,7 +2747,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -2598,6 +2798,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2608,12 +2815,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2651,7 +2865,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2694,22 +2908,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2814,8 +3029,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2947,19 +3162,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -4024,23 +4240,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Biểu đồ 1">
+        <xdr:cNvPr id="3" name="Biểu đồ 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E08C5268-7F66-4CF6-79BE-C1767E4DEB9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0969B02-A7F4-BBF0-37B4-0DB10CFCE16E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4065,16 +4281,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4106,16 +4322,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>500062</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>309562</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>195262</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12971,7 +13187,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED39DD2-7963-4AF2-9E45-43E8633653CC}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -12980,91 +13196,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" t="s">
         <v>406</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>81</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2">
         <v>61.83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" t="s">
         <v>407</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>13</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3">
         <v>9.92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" t="s">
         <v>408</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4">
         <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" t="s">
         <v>409</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>11</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5">
         <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" t="s">
         <v>410</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>9</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>6.87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" t="s">
         <v>411</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>2.29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" t="s">
         <v>412</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8">
         <v>2.29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -13075,51 +13327,89 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0007BBAE-29B6-40E7-9EEA-BC404190DD0F}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" t="s">
         <v>307</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>9</v>
       </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13136,18 +13426,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>131</v>
       </c>
     </row>
@@ -13159,18 +13449,106 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED6C4CD-7A65-4E47-9511-02EE709DD43B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="76.7109375" customWidth="1"/>
+    <col min="1" max="1" width="76.7109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>414</v>
-      </c>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="9"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I20" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>